--- a/public/sap-reporting/expansion-150-downloads/EXT-PP16-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP16-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R3951c74039ba453a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R2d455ebd93d54016"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Re0c5af1bac1f423b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R14750c3fce2c4977"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R8db81c4e59fa4fdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rb697f300ecf54a7a"/>
   </x:sheets>
 </x:workbook>
 </file>
